--- a/Result/profitability/8043.xlsx
+++ b/Result/profitability/8043.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38875</v>
+        <v>0.4012500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4725</v>
+        <v>5.74</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4012500000000001</v>
+        <v>0.44875</v>
       </c>
       <c r="N3" t="n">
-        <v>6.06625</v>
+        <v>6.322500000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.91</v>
       </c>
       <c r="M4" t="n">
-        <v>0.51875</v>
+        <v>0.6012500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>6.600000000000001</v>
+        <v>6.711250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58875</v>
+        <v>0.6887500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>6.65625</v>
+        <v>7.27125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.69125</v>
+        <v>0.62875</v>
       </c>
       <c r="N6" t="n">
-        <v>7.27375</v>
+        <v>7.4825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.63</v>
+        <v>0.475</v>
       </c>
       <c r="N7" t="n">
-        <v>7.73</v>
+        <v>7.4675</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.49125</v>
+        <v>0.36625</v>
       </c>
       <c r="N8" t="n">
-        <v>7.766249999999999</v>
+        <v>7.70375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8043</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1764</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1647</v>
+      </c>
+      <c r="E75" t="n">
+        <v>116</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>28</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>37</v>
+      </c>
+      <c r="K75" t="n">
+        <v>28</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.47625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7407407407407407</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07032348804500699</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.777777777777778</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.911242603550296</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
